--- a/九龙-九龙塘-Park College/Park College_销控明细表.xlsx
+++ b/九龙-九龙塘-Park College/Park College_销控明细表.xlsx
@@ -1428,7 +1428,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1713,7 +1713,7 @@
           <t>GV | 3060呎 (4+房)
 $14880万
 $48,627/呎
-(26年-08月-19日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
     </row>

--- a/九龙-九龙塘-Park College/Park College_销控明细表.xlsx
+++ b/九龙-九龙塘-Park College/Park College_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -119,12 +119,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -202,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -265,9 +259,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1155,23 +1146,19 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>41012</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1180,12 +1167,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1195,7 +1182,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1521,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -1544,7 +1531,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -1666,12 +1653,12 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 1463呎 (3房)
-招标单位
--
-(在售)</t>
+$6000万
+$41,012/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr"/>
